--- a/data/cennik.xlsx
+++ b/data/cennik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Repository\Ostrzomat\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F7A31C-534E-442B-807D-D30980F3116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D28AFF-F1CF-4A78-AC10-F99E5D17D9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2415" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,7 +614,7 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>62.4</v>
+        <v>64.5</v>
       </c>
       <c r="H4">
         <v>49.1</v>

--- a/data/cennik.xlsx
+++ b/data/cennik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Repository\Ostrzomat\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D28AFF-F1CF-4A78-AC10-F99E5D17D9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510EF199-1675-4C1F-AD62-E9E473004ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2415" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
